--- a/ValueSet-mii-vs-prozedur-ops.xlsx
+++ b/ValueSet-mii-vs-prozedur-ops.xlsx
@@ -23,12 +23,13 @@
     <sheet name="Include #13" r:id="rId17" sheetId="15"/>
     <sheet name="Include #14" r:id="rId18" sheetId="16"/>
     <sheet name="Include #15" r:id="rId19" sheetId="17"/>
+    <sheet name="Include #16" r:id="rId20" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2026.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,6 +104,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define OPS codes allowed for procedure coding.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -370,22 +374,24 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -404,28 +410,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -444,28 +450,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -484,28 +490,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -524,28 +530,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -564,28 +570,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -604,28 +610,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -644,28 +650,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -684,28 +690,68 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -724,28 +770,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -764,28 +810,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -804,28 +850,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -844,28 +890,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -884,28 +930,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -924,28 +970,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -964,28 +1010,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1004,28 +1050,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-mii-vs-prozedur-ops.xlsx
+++ b/ValueSet-mii-vs-prozedur-ops.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -76,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-prozedur-ops.xlsx
+++ b/ValueSet-mii-vs-prozedur-ops.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -100,7 +100,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Enthaelt OPS-Codes der Versionen 2010 bis 2025</t>
+    <t>Enthaelt OPS-Codes der aller verfügbarer Versionen</t>
   </si>
   <si>
     <t>Purpose</t>
